--- a/server/data.xlsx
+++ b/server/data.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Contact" sheetId="1" r:id="rId1"/>
+    <sheet name="Feedback" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,6 +398,117 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Subject</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Message</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Date</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Jeevaa M M</v>
+      </c>
+      <c r="B2" t="str">
+        <v>jeevaamarimuthu8@gmail.com</v>
+      </c>
+      <c r="C2" t="str">
+        <v>06380372501</v>
+      </c>
+      <c r="D2" t="str">
+        <v>chapathi</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v>14/3/2026, 10:04:25 am</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>jeevaa</v>
+      </c>
+      <c r="B3" t="str">
+        <v>jeevaamarimuthu8@gmail.com</v>
+      </c>
+      <c r="C3" t="str">
+        <v>6380372501</v>
+      </c>
+      <c r="D3" t="str">
+        <v>chapathi</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>14/3/2026, 10:09:51 am</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>abhi</v>
+      </c>
+      <c r="B4" t="str">
+        <v>jeevaamarimuthu8@gmail.com</v>
+      </c>
+      <c r="C4" t="str">
+        <v>06380372501</v>
+      </c>
+      <c r="D4" t="str">
+        <v>idli</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>14/3/2026, 10:11:59 am</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>kamal</v>
+      </c>
+      <c r="B5" t="str">
+        <v>jeevaamarimuthu9@gmail.com</v>
+      </c>
+      <c r="C5" t="str">
+        <v>6380372501</v>
+      </c>
+      <c r="D5" t="str">
+        <v>readymade food</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>14/3/2026, 11:04:48 am</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
@@ -404,16 +516,16 @@
         <v>Name</v>
       </c>
       <c r="B1" t="str">
-        <v>Email</v>
+        <v>Location</v>
       </c>
       <c r="C1" t="str">
-        <v>Phone</v>
+        <v>Product</v>
       </c>
       <c r="D1" t="str">
-        <v>Subject</v>
+        <v>Rating</v>
       </c>
       <c r="E1" t="str">
-        <v>Message</v>
+        <v>Comment</v>
       </c>
       <c r="F1" t="str">
         <v>Date</v>
@@ -421,42 +533,42 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jeevaa M M</v>
+        <v>jeevaa</v>
       </c>
       <c r="B2" t="str">
-        <v>jeevaamarimuthu8@gmail.com</v>
+        <v>salem</v>
       </c>
       <c r="C2" t="str">
-        <v>06380372501</v>
-      </c>
-      <c r="D2" t="str">
-        <v>chapathi</v>
+        <v>idly</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>good</v>
       </c>
       <c r="F2" t="str">
-        <v>14/3/2026, 10:04:25 am</v>
+        <v>14/3/2026, 10:59:51 am</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>jeevaa</v>
+        <v>mukesh</v>
       </c>
       <c r="B3" t="str">
-        <v>jeevaamarimuthu8@gmail.com</v>
+        <v>pallipalayam</v>
       </c>
       <c r="C3" t="str">
-        <v>6380372501</v>
-      </c>
-      <c r="D3" t="str">
         <v>chapathi</v>
       </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
       <c r="E3" t="str">
-        <v/>
+        <v>good</v>
       </c>
       <c r="F3" t="str">
-        <v>14/3/2026, 10:09:51 am</v>
+        <v>14/3/2026, 11:06:17 am</v>
       </c>
     </row>
     <row r="4">
@@ -464,19 +576,19 @@
         <v>abhi</v>
       </c>
       <c r="B4" t="str">
-        <v>jeevaamarimuthu8@gmail.com</v>
+        <v>erode</v>
       </c>
       <c r="C4" t="str">
-        <v>06380372501</v>
-      </c>
-      <c r="D4" t="str">
-        <v>idli</v>
+        <v>chapathi</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>good</v>
       </c>
       <c r="F4" t="str">
-        <v>14/3/2026, 10:11:59 am</v>
+        <v>14/3/2026, 11:09:02 am</v>
       </c>
     </row>
   </sheetData>
